--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129763750</v>
+        <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>100957</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444976</v>
+        <v>444966</v>
       </c>
       <c r="R4" t="n">
-        <v>7039209</v>
+        <v>7039210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129763748</v>
+        <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>92542</v>
+        <v>100958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444966</v>
+        <v>444976</v>
       </c>
       <c r="R5" t="n">
         <v>7039209</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105819</v>
+        <v>105820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>444966</v>
       </c>
       <c r="R10" t="n">
-        <v>7039209</v>
+        <v>7039210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105820</v>
+        <v>105825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129763748</v>
+        <v>129763750</v>
       </c>
       <c r="B4" t="n">
-        <v>92548</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444966</v>
+        <v>444976</v>
       </c>
       <c r="R4" t="n">
-        <v>7039210</v>
+        <v>7039209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129763750</v>
+        <v>129763748</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>92548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444976</v>
+        <v>444966</v>
       </c>
       <c r="R5" t="n">
-        <v>7039209</v>
+        <v>7039210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129763750</v>
+        <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>92548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444976</v>
+        <v>444966</v>
       </c>
       <c r="R4" t="n">
-        <v>7039209</v>
+        <v>7039210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129763748</v>
+        <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>92548</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444966</v>
+        <v>444976</v>
       </c>
       <c r="R5" t="n">
-        <v>7039210</v>
+        <v>7039209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129763748</v>
+        <v>129763750</v>
       </c>
       <c r="B4" t="n">
-        <v>92548</v>
+        <v>100967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444966</v>
+        <v>444976</v>
       </c>
       <c r="R4" t="n">
-        <v>7039210</v>
+        <v>7039209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129763750</v>
+        <v>129763748</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>92552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444976</v>
+        <v>444966</v>
       </c>
       <c r="R5" t="n">
-        <v>7039209</v>
+        <v>7039210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105825</v>
+        <v>105829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763750</v>
       </c>
       <c r="B4" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763748</v>
       </c>
       <c r="B5" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105829</v>
+        <v>105831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129763750</v>
+        <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>92554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444976</v>
+        <v>444966</v>
       </c>
       <c r="R4" t="n">
-        <v>7039209</v>
+        <v>7039210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129763748</v>
+        <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>92554</v>
+        <v>100969</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444966</v>
+        <v>444976</v>
       </c>
       <c r="R5" t="n">
-        <v>7039210</v>
+        <v>7039209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105831</v>
+        <v>105841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96016</v>
+        <v>96020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105841</v>
+        <v>105845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96020</v>
+        <v>96023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105845</v>
+        <v>105848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96023</v>
+        <v>96024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105848</v>
+        <v>105849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92561</v>
+        <v>92578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96024</v>
+        <v>96041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105849</v>
+        <v>105866</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>91776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92594</v>
+        <v>92735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>101020</v>
+        <v>101163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91635</v>
+        <v>91772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96057</v>
+        <v>96200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>105882</v>
+        <v>106026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92357</v>
+        <v>92498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>101020</v>
+        <v>101163</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>444966</v>
       </c>
       <c r="R10" t="n">
-        <v>7039210</v>
+        <v>7039209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>444966</v>
       </c>
       <c r="R10" t="n">
-        <v>7039209</v>
+        <v>7039210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129763755</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129763760</v>
       </c>
       <c r="B3" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129763750</v>
       </c>
       <c r="B5" t="n">
-        <v>101216</v>
+        <v>101217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129763756</v>
       </c>
       <c r="B6" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129763747</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129763757</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129763751</v>
       </c>
       <c r="B9" t="n">
-        <v>96234</v>
+        <v>96235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129763749</v>
       </c>
       <c r="B10" t="n">
-        <v>106113</v>
+        <v>106114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129763754</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129763753</v>
       </c>
       <c r="B12" t="n">
-        <v>92531</v>
+        <v>92532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129763741</v>
       </c>
       <c r="B13" t="n">
-        <v>101216</v>
+        <v>101217</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129763746</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53766-2025 artfynd.xlsx
+++ b/artfynd/A 53766-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129763755</v>
+        <v>129763751</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445026</v>
+        <v>444979</v>
       </c>
       <c r="R2" t="n">
-        <v>7039227</v>
+        <v>7039202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129763760</v>
+        <v>129763753</v>
       </c>
       <c r="B3" t="n">
-        <v>91810</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445083</v>
+        <v>444972</v>
       </c>
       <c r="R3" t="n">
-        <v>7039128</v>
+        <v>7039201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>129763748</v>
       </c>
       <c r="B4" t="n">
-        <v>92769</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129763750</v>
+        <v>129763754</v>
       </c>
       <c r="B5" t="n">
-        <v>101217</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444976</v>
+        <v>444967</v>
       </c>
       <c r="R5" t="n">
-        <v>7039209</v>
+        <v>7039202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129763756</v>
+        <v>129763749</v>
       </c>
       <c r="B6" t="n">
-        <v>91806</v>
+        <v>106228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445023</v>
+        <v>444966</v>
       </c>
       <c r="R6" t="n">
-        <v>7039224</v>
+        <v>7039210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129763747</v>
+        <v>129763750</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>101325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445023</v>
+        <v>444976</v>
       </c>
       <c r="R7" t="n">
-        <v>7039275</v>
+        <v>7039209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129763757</v>
+        <v>129763756</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445038</v>
+        <v>445023</v>
       </c>
       <c r="R8" t="n">
-        <v>7039201</v>
+        <v>7039224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129763751</v>
+        <v>129763760</v>
       </c>
       <c r="B9" t="n">
-        <v>96235</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444979</v>
+        <v>445083</v>
       </c>
       <c r="R9" t="n">
-        <v>7039202</v>
+        <v>7039128</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129763749</v>
+        <v>129763738</v>
       </c>
       <c r="B10" t="n">
-        <v>106114</v>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444966</v>
+        <v>445333</v>
       </c>
       <c r="R10" t="n">
-        <v>7039210</v>
+        <v>7039400</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763754</v>
+        <v>129763740</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444967</v>
+        <v>445344</v>
       </c>
       <c r="R11" t="n">
-        <v>7039202</v>
+        <v>7039393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763753</v>
+        <v>129763762</v>
       </c>
       <c r="B12" t="n">
-        <v>92532</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444972</v>
+        <v>445336</v>
       </c>
       <c r="R12" t="n">
-        <v>7039201</v>
+        <v>7039420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129763741</v>
+        <v>129763746</v>
       </c>
       <c r="B13" t="n">
-        <v>101217</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445269</v>
+        <v>445113</v>
       </c>
       <c r="R13" t="n">
-        <v>7039385</v>
+        <v>7039345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129763746</v>
+        <v>129763747</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445113</v>
+        <v>445023</v>
       </c>
       <c r="R14" t="n">
-        <v>7039345</v>
+        <v>7039275</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,6 +2063,648 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129763755</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>445026</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7039227</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129763757</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>445038</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7039201</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129763758</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>445040</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7039188</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129763761</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>445315</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7039364</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129763741</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>445269</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7039385</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129763763</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>445336</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7039418</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
